--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -684,25 +684,25 @@
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 261026억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 261025억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 262360억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 263179억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 261074억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 261873억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 258876억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+고객지수 4분기 이동합(t−4) 259656억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -936,13 +936,13 @@
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 111624억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 111630억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 113070억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 113081억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -2031,25 +2031,25 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 261026억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 261025억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 262360억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 263179억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 261074억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 261873억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 258876억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 고객지수 4분기 이동합(t−4) 259656억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2498,13 +2498,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 111624억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 111630억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 113070억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 113081억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -7019,23 +7019,23 @@
         <v>0.636736</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.46629</v>
+        <v>0.466289</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.447913</v>
+        <v>0.44791</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.326727</v>
+        <v>0.32672</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.200212</v>
+        <v>0.203957</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.086131</v>
+        <v>0.08945599999999999</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.016986</v>
+        <v>0.020052</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7613,10 +7613,10 @@
         <v>-324.5</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-323.89</v>
+        <v>-323.88</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-321.89</v>
+        <v>-321.87</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8062,7 +8062,7 @@
         <v>0.270003</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.269999</v>
+        <v>0.270001</v>
       </c>
       <c r="AI28" s="24" t="n">
         <v>0.270001</v>
@@ -8072,16 +8072,16 @@
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
+        <v>0.269997</v>
+      </c>
+      <c r="AL28" s="24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AM28" s="24" t="n">
         <v>0.270001</v>
       </c>
-      <c r="AL28" s="24" t="n">
+      <c r="AN28" s="24" t="n">
         <v>0.270001</v>
-      </c>
-      <c r="AM28" s="24" t="n">
-        <v>0.269998</v>
-      </c>
-      <c r="AN28" s="24" t="n">
-        <v>0.269999</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8563,20 +8563,20 @@
         <v>0.282834</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.27882</v>
+        <v>0.278816</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.211236</v>
+        <v>0.211228</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.13699</v>
+        <v>0.139552</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.059717</v>
+        <v>0.062021</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.011971</v>
+        <v>0.014134</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8816,23 +8816,23 @@
         <v>1103.13</v>
       </c>
       <c r="AH34" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AI34" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ34" s="30" t="n"/>
       <c r="AK34" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL34" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AM34" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO34" s="30" t="n"/>
     </row>
@@ -8944,23 +8944,23 @@
         <v>1103.13</v>
       </c>
       <c r="AH35" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AI35" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="30" t="n"/>
       <c r="AK35" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL35" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AM35" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO35" s="30" t="n"/>
     </row>
@@ -9203,20 +9203,20 @@
         <v>-0.034679</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>-0.038319</v>
+        <v>-0.038318</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
         <v>-0.040641</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>-0.013107</v>
+        <v>-0.01327</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>-0.04357</v>
+        <v>-0.04373</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>-0.045018</v>
+        <v>-0.045189</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9338,13 +9338,13 @@
         <v>0.012979</v>
       </c>
       <c r="AL38" s="24" t="n">
-        <v>0.003964</v>
+        <v>0.004013</v>
       </c>
       <c r="AM38" s="24" t="n">
-        <v>0.012953</v>
+        <v>0.012998</v>
       </c>
       <c r="AN38" s="24" t="n">
-        <v>0.012637</v>
+        <v>0.01268</v>
       </c>
       <c r="AO38" s="25" t="n"/>
     </row>
@@ -9996,13 +9996,13 @@
         <v>4.776786</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.299429</v>
+        <v>-0.300571</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.231065</v>
+        <v>-0.232349</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.15</v>
+        <v>-0.151429</v>
       </c>
       <c r="AO44" s="25" t="n"/>
     </row>

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$101</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$111</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 163931억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 175806억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 196744억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 218595억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 240370억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 254552억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 261025억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 263179억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 261873억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 259656억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)</t>
+전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 6.8% 유지</t>
+최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,55 +894,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 105002억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 104765억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 105895억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 105315억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 106910억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 105901억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 107053억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 105474억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 108362억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 106059억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 109759억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 106611억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 111184억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 107199억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 111630억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 106774억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 113081억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 107361억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1995,61 +1995,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 163931억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 175806억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 196744억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 218595억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.2%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 240370억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 254552억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 261025억 × 비례계수 0.5183 × 계절비중 Q1 0.245(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 263179억 × 비례계수 0.5183 × 계절비중 Q2 0.261(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 261873억 × 비례계수 0.5183 × 계절비중 Q3 0.248(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 259656억 × 비례계수 0.5183 × 계절비중 Q4 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.63, n=12, 창 12)
+        <t>추정: 전년동기 × (1+0.1%) — g=최근 4분기 합 YoY 0.2% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -2235,61 +2235,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2390,61 +2390,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 6.8% 유지
+        <t>추정: 최근 8분기 OPM 중위 6.8% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2456,55 +2456,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 105002억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 104765억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 105895억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 105315억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 106910억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 105901억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 107053억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 105474억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 108362억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 106059억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 109759억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 106611억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 111184억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 107199억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 111630억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 106774억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 113081억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 107361억 × 0.55% − 총차입금 52655억 × 3.63% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4830,7 +4830,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4951,14 +4951,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 일회성 의심 2026Q2: 비영업손익 36,305억(영업이익 1,289억의 28배, 12분기 중위 2,244억) → 지배NI 28,392억·EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함)</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 32.2% &gt; 추세 3.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.63 유의)): 전년동기 × (1+g) 추세 / 일회성 의심 2026Q2: 비영업손익 36,305억(영업이익 1,289억의 28배, 12분기 중위 2,244억) → 지배NI 28,392억·EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 32.2, "op_wape_pct": 43.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 20450.78, "rev_act": 16228.33, "op_pred": 1349.61, "op_act": 1172.64}, {"q": "2025Q4", "rev_pred": 21141.06, "rev_act": 15564.18, "op_pred": 1395.17, "op_act": 665.27}, {"q": "2026Q1", "rev_pred": 21947.17, "rev_act": 16264.0, "op_pred": 1448.37, "op_act": 881.28}, {"q": "2026Q2", "rev_pred": 23848.0, "rev_act": 18060.19, "op_pred": 1573.81, "op_act": 1288.84}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 3.6, "op_wape_pct": 21.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 22.5, "wape_trend": 3.9, "adopted": false}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 16578.27, "rev_act": 16228.33, "op_pred": 1094.05, "op_act": 1172.64}, {"q": "2025Q4", "rev_pred": 16814.11, "rev_act": 15564.18, "op_pred": 1109.62, "op_act": 665.27}, {"q": "2026Q1", "rev_pred": 16224.2, "rev_act": 16264.0, "op_pred": 1070.69, "op_act": 881.28}, {"q": "2026Q2", "rev_pred": 17299.1, "rev_act": 18060.19, "op_pred": 1141.62, "op_act": 1288.84}]}</t>
         </is>
       </c>
     </row>
@@ -7006,36 +7006,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.296041</v>
+        <v>0.00234</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.445282</v>
+        <v>0.00234</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.534146</v>
+        <v>0.00234</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.636736</v>
+        <v>0.00234</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.466289</v>
+        <v>0.001171</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.44791</v>
+        <v>0.00117</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.32672</v>
+        <v>0.00117</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.203957</v>
+        <v>0.00117</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.08945599999999999</v>
+        <v>0.000585</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.020052</v>
+        <v>0.000585</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7584,39 +7584,39 @@
         <v>-334.19</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>-333.06</v>
+        <v>-333.39</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-331.82</v>
+        <v>-332.62</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-330.42</v>
+        <v>-331.81</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-330.22</v>
+        <v>-332.4</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-328.41</v>
+        <v>-331.59</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-326.47</v>
+        <v>-330.83</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>-324.5</v>
+        <v>-330.02</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-323.88</v>
+        <v>-330.6</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-321.87</v>
+        <v>-329.79</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8046,42 +8046,42 @@
         <v/>
       </c>
       <c r="AC28" s="24" t="n">
-        <v>0.270003</v>
+        <v>0.27</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.269997</v>
+        <v>0.27</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG28" s="24" t="n">
+        <v>0.269994</v>
+      </c>
+      <c r="AH28" s="24" t="n">
+        <v>0.269998</v>
+      </c>
+      <c r="AI28" s="24" t="n">
         <v>0.270002</v>
-      </c>
-      <c r="AG28" s="24" t="n">
-        <v>0.270003</v>
-      </c>
-      <c r="AH28" s="24" t="n">
-        <v>0.270001</v>
-      </c>
-      <c r="AI28" s="24" t="n">
-        <v>0.270001</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.269997</v>
+        <v>0.269995</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.27</v>
+        <v>0.270003</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.270001</v>
+        <v>0.269996</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.270001</v>
+        <v>0.269994</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8547,36 +8547,36 @@
         <v/>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>-4.912645</v>
+        <v>-4.374832</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>-0.45719</v>
+        <v>-0.560745</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.443722</v>
+        <v>0.120168</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.331109</v>
+        <v>-0.021905</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.282834</v>
+        <v>0.000634</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.278816</v>
+        <v>0.000623</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.211228</v>
+        <v>0.000638</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.139552</v>
+        <v>0.000672</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.062021</v>
+        <v>0.000319</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.014134</v>
+        <v>0.000317</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8810,29 +8810,29 @@
       </c>
       <c r="AE34" s="30" t="n"/>
       <c r="AF34" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AG34" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AH34" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="30" t="n"/>
       <c r="AK34" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL34" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AM34" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN34" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO34" s="30" t="n"/>
     </row>
@@ -8938,29 +8938,29 @@
       </c>
       <c r="AE35" s="30" t="n"/>
       <c r="AF35" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AG35" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AH35" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" s="30" t="n"/>
       <c r="AK35" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL35" s="29" t="n">
         <v>1103.13</v>
       </c>
       <c r="AM35" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN35" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO35" s="30" t="n"/>
     </row>
@@ -9187,36 +9187,36 @@
         <v/>
       </c>
       <c r="AC37" s="24" t="n">
-        <v>-0.02017</v>
+        <v>-0.014345</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>-0.02243</v>
+        <v>-0.013743</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>-0.026103</v>
+        <v>-0.014831</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>-0.003761</v>
+        <v>0.010985</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>-0.034679</v>
+        <v>-0.014873</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>-0.038318</v>
+        <v>-0.014259</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>-0.040641</v>
+        <v>-0.015393</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>-0.01327</v>
+        <v>0.011301</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>-0.04373</v>
+        <v>-0.015429</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>-0.045189</v>
+        <v>-0.014802</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9315,36 +9315,36 @@
         <v/>
       </c>
       <c r="AC38" s="24" t="n">
-        <v>0.007866</v>
+        <v>0.005594</v>
       </c>
       <c r="AD38" s="24" t="n">
-        <v>0.008503999999999999</v>
+        <v>0.005253</v>
       </c>
       <c r="AE38" s="25" t="n"/>
       <c r="AF38" s="24" t="n">
-        <v>0.009593000000000001</v>
+        <v>0.005562</v>
       </c>
       <c r="AG38" s="24" t="n">
-        <v>0.001333</v>
+        <v>-0.004036</v>
       </c>
       <c r="AH38" s="24" t="n">
-        <v>0.012231</v>
+        <v>0.005547</v>
       </c>
       <c r="AI38" s="24" t="n">
-        <v>0.012888</v>
+        <v>0.00521</v>
       </c>
       <c r="AJ38" s="25" t="n"/>
       <c r="AK38" s="24" t="n">
-        <v>0.012979</v>
+        <v>0.005515</v>
       </c>
       <c r="AL38" s="24" t="n">
-        <v>0.004013</v>
+        <v>-0.003965</v>
       </c>
       <c r="AM38" s="24" t="n">
-        <v>0.012998</v>
+        <v>0.005496</v>
       </c>
       <c r="AN38" s="24" t="n">
-        <v>0.01268</v>
+        <v>0.005163</v>
       </c>
       <c r="AO38" s="25" t="n"/>
     </row>
@@ -9973,36 +9973,36 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>-0.571429</v>
+        <v>-0.567227</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>-0.457286</v>
+        <v>-0.447236</v>
       </c>
       <c r="AE44" s="25" t="n"/>
       <c r="AF44" s="24" t="n">
-        <v>-0.481481</v>
+        <v>-0.462963</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>7.101852</v>
+        <v>12.453704</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>6.637255</v>
+        <v>13.087379</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>5.481481</v>
+        <v>12.181818</v>
       </c>
       <c r="AJ44" s="25" t="n"/>
       <c r="AK44" s="24" t="n">
-        <v>4.776786</v>
+        <v>11.491379</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.300571</v>
+        <v>-0.004129</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.232349</v>
+        <v>-0.003446</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.151429</v>
+        <v>-0.003448</v>
       </c>
       <c r="AO44" s="25" t="n"/>
     </row>
@@ -10105,23 +10105,23 @@
         <v>-0.138889</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>-0.032258</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>-0.032258</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="25" t="n"/>
       <c r="AK45" s="24" t="n">
-        <v>-0.032258</v>
+        <v>0</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>-0.032258</v>
+        <v>0</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>-0.033333</v>
+        <v>0</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>-0.033333</v>
+        <v>0</v>
       </c>
       <c r="AO45" s="25" t="n"/>
     </row>
@@ -10923,7 +10923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18105,16 +18105,47 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="K77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="U77" s="9" t="n"/>
-      <c r="Z77" s="9" t="n"/>
+      <c r="Q77" s="18" t="n">
+        <v>9658.65</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>9246.040000000001</v>
+      </c>
+      <c r="S77" s="18" t="n">
+        <v>7984.59</v>
+      </c>
+      <c r="T77" s="18" t="n">
+        <v>9140.559999999999</v>
+      </c>
+      <c r="U77" s="34" t="n">
+        <v>36029.84</v>
+      </c>
+      <c r="V77" s="18" t="n">
+        <v>4696.69</v>
+      </c>
+      <c r="W77" s="18" t="n">
+        <v>5184</v>
+      </c>
+      <c r="X77" s="18" t="n">
+        <v>6840.08</v>
+      </c>
+      <c r="Y77" s="18" t="n">
+        <v>6399.41</v>
+      </c>
+      <c r="Z77" s="34" t="n">
+        <v>23120.18</v>
+      </c>
+      <c r="AA77" s="18" t="n">
+        <v>9435.26</v>
+      </c>
       <c r="AB77" s="19" t="n">
-        <v>-3631.75</v>
+        <v>9730.049999999999</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -18136,78 +18167,47 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>189767.52</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>-76357.97</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>36313.96</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>206935.87</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>217674.51</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>384566.37</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>19425.33</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>265160.35</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>176899.91</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>326780.74</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>788266.33</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
       <c r="Q78" s="18" t="n">
-        <v>113737.76</v>
+        <v>48061.81</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>209889</v>
+        <v>0</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>134088.68</v>
+        <v>458.48</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>139085.85</v>
+        <v>0</v>
       </c>
       <c r="U78" s="34" t="n">
-        <v>596801.29</v>
+        <v>48520.29</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>109138.48</v>
+        <v>62913.24</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>167174.14</v>
+        <v>0</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>135288.72</v>
+        <v>9216.450000000001</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>377876.14</v>
+        <v>110.77</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>789477.48</v>
+        <v>72240.46000000001</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>85181.96000000001</v>
+        <v>78278.22</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>30910.52</v>
+        <v>475.31</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -18229,78 +18229,47 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>7231.1</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>6904.18</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>6495.89</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>6792.9</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>7437.76</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>27630.73</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>7069.9</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>7034.24</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>7209.64</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>10742.84</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>32056.62</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
       <c r="Q79" s="18" t="n">
-        <v>7059.71</v>
+        <v>-66011.17</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>7315.32</v>
+        <v>-92351.53999999999</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>7351.83</v>
+        <v>-94206.83</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>6808.32</v>
+        <v>-95237.00999999999</v>
       </c>
       <c r="U79" s="34" t="n">
-        <v>28535.18</v>
+        <v>-347806.55</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>103182.77</v>
+        <v>-78864.28999999999</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>97615.25</v>
+        <v>-78934.92999999999</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>-177546.86</v>
+        <v>-90252.5</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>386321.79</v>
+        <v>-91793.28</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>409572.95</v>
+        <v>-339845</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>93709.35000000001</v>
+        <v>-72288.52</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>91886.07000000001</v>
+        <v>-75403.96000000001</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -18322,78 +18291,47 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>10316.76</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>9633.33</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>10783.43</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>11943.51</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>11017.5</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>43377.77</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>15455.79</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>11241.46</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>11390.85</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>8506.49</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>46594.59</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
       <c r="Q80" s="18" t="n">
-        <v>12560.41</v>
+        <v>28985.2</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>11918.19</v>
+        <v>29021.28</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>11597.57</v>
+        <v>14401.43</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>12238.65</v>
+        <v>66663.8</v>
       </c>
       <c r="U80" s="34" t="n">
-        <v>48314.82</v>
+        <v>139071.71</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>12507.98</v>
+        <v>15900.6</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>12137.41</v>
+        <v>38399.63</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>11921.41</v>
+        <v>25574.32</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>12821.84</v>
+        <v>33953.29</v>
       </c>
       <c r="Z80" s="34" t="n">
-        <v>49388.64</v>
+        <v>113827.84</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>11707.12</v>
+        <v>21180.12</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>12427.34</v>
+        <v>42412.63</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -18415,78 +18353,47 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>59809.67</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-51434.55</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-51879.03</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-54912.15</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-15171.01</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-173396.74</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-52806.03</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>-34801.84</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-29351.47</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>-33724.33</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>-150683.67</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
       <c r="Q81" s="18" t="n">
-        <v>-25539.05</v>
+        <v>-11995.86</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>-41834.59</v>
+        <v>-10360.83</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>-37308.76</v>
+        <v>-23805.76</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>-28225.56</v>
+        <v>-16623.5</v>
       </c>
       <c r="U81" s="34" t="n">
-        <v>-132907.96</v>
+        <v>-62785.95</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>-96171.84</v>
+        <v>-19009.53</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>-83723.16</v>
+        <v>-35308.93</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>-53013.38</v>
+        <v>-31992.77</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>-44772.23</v>
+        <v>-10033.54</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>-277680.61</v>
+        <v>-96344.77</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>-61617.87</v>
+        <v>-11180.82</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>-9135.620000000001</v>
+        <v>-18254.8</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -18508,78 +18415,47 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>390031.95</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-447113.88</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-95715.22</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>401282.92</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>177631.35</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>36085.17</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-128460.36</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-83739.69</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-89760.59</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-53380.52</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>-355341.16</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
       <c r="Q82" s="18" t="n">
-        <v>-72833.17999999999</v>
+        <v>45192.81</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>507010.91</v>
+        <v>53139.72</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>-105491.96</v>
+        <v>-65314.42</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>-47148.44</v>
+        <v>82531.74000000001</v>
       </c>
       <c r="U82" s="34" t="n">
-        <v>281537.33</v>
+        <v>115549.85</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>-89288.97</v>
+        <v>37598.45</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>146540.07</v>
+        <v>34797.71</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>105710.03</v>
+        <v>-4647.71</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>106421.83</v>
+        <v>13358.45</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>269382.96</v>
+        <v>81106.89999999999</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-109480.52</v>
+        <v>68669.38</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>67983.59</v>
+        <v>3281.19</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -18601,78 +18477,47 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>102819.66</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>72229.7</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>87111.85000000001</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>101693.09</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>123706.92</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>384741.56</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>114720.08</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>70988.73</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>125619.7</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>67680.85000000001</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>379009.36</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
       <c r="Q83" s="18" t="n">
-        <v>55864.07</v>
+        <v>-34257.71</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>72825.24000000001</v>
+        <v>-38852.34</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>64949.2</v>
+        <v>11325.64</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>64081.33</v>
+        <v>-28984.04</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>257719.84</v>
+        <v>-90768.45</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>91179.11</v>
+        <v>-49263.89</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>46925.54</v>
+        <v>-79895.00999999999</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>73752.25999999999</v>
+        <v>18387.65</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>108048.61</v>
+        <v>-36312.17</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>319905.52</v>
+        <v>-147083.42</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>94238.32000000001</v>
+        <v>-85101.69</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>83596.02</v>
+        <v>-27940.25</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -18694,78 +18539,47 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>104133.59</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>72627.46000000001</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>89907.98</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>105056.71</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>125439.45</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>393031.6</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>120787.53</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>73053.42999999999</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>126554.27</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>69451.98</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>389847.21</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
       <c r="Q84" s="18" t="n">
-        <v>57157.04</v>
+        <v>6756.51</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>74065.75</v>
+        <v>9901.809999999999</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>65508.53</v>
+        <v>-65.06</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>68269.3</v>
+        <v>6212.8</v>
       </c>
       <c r="U84" s="34" t="n">
-        <v>265000.62</v>
+        <v>22806.06</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>92403.92</v>
+        <v>5394.59</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>48155.14</v>
+        <v>1069.6</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>75674.07000000001</v>
+        <v>5330.21</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>114486.52</v>
+        <v>5064.25</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>330719.65</v>
+        <v>16858.65</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>95027.00999999999</v>
+        <v>122157.76</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>84402.91</v>
+        <v>51127.49</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -18787,78 +18601,47 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>1313.93</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>397.76</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>2796.13</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>3363.62</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>1732.53</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>8290.040000000001</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>6067.45</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>2064.7</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>934.5700000000001</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>1771.13</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>10837.85</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
       <c r="Q85" s="18" t="n">
-        <v>1292.97</v>
+        <v>-5403.71</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1240.51</v>
+        <v>-5059.23</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>559.33</v>
+        <v>-2882</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>4187.97</v>
+        <v>-905.11</v>
       </c>
       <c r="U85" s="34" t="n">
-        <v>7280.78</v>
+        <v>-14250.05</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>1224.81</v>
+        <v>-1492.13</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>1229.6</v>
+        <v>-163.96</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>1921.81</v>
+        <v>-73656.39999999999</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>6437.91</v>
+        <v>19085.1</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>10814.13</v>
+        <v>-56227.39</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>788.6900000000001</v>
+        <v>-13246.43</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>806.89</v>
+        <v>-5429.36</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -18880,70 +18663,47 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>806.04</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>705.9299999999999</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>2943.72</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>508.07</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>2019.59</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>6177.31</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>45146.72</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>8482.85</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
       <c r="P86" s="9" t="n"/>
       <c r="Q86" s="18" t="n">
-        <v>788.05</v>
+        <v>75669.82000000001</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>820.5700000000001</v>
+        <v>101597.58</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>1244.14</v>
+        <v>102191.42</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>4274.97</v>
+        <v>104377.57</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>7127.73</v>
+        <v>383836.39</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>336.63</v>
+        <v>83560.98</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>1113.85</v>
+        <v>84118.92999999999</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>5295.68</v>
+        <v>97092.58</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>25821.38</v>
+        <v>98192.69</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>32567.54</v>
+        <v>362965.18</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>1031.43</v>
+        <v>81723.78</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>451.46</v>
+        <v>85134.00999999999</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -18965,57 +18725,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>0</v>
+          <t>중단사업이익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>2150</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>2150.22</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>8.32</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="S87" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>5.84</v>
-      </c>
       <c r="U87" s="9" t="n"/>
-      <c r="V87" s="18" t="n">
-        <v>92.25</v>
-      </c>
-      <c r="X87" s="18" t="n">
-        <v>208.14</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>75937.03999999999</v>
-      </c>
       <c r="Z87" s="9" t="n"/>
-      <c r="AA87" s="18" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AB87" s="19" t="n">
-        <v>0.49</v>
+        <v>-3631.75</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -19037,78 +18756,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-732.52</v>
+        <v>189767.52</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>530.49</v>
+        <v>-76357.97</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>729.63</v>
+        <v>36313.96</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>1381.32</v>
+        <v>206935.87</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>3996.46</v>
+        <v>217674.51</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>6637.9</v>
+        <v>384566.37</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>9399.700000000001</v>
+        <v>19425.33</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>7308.47</v>
+        <v>265160.35</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>8080.09</v>
+        <v>176899.91</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>10292.59</v>
+        <v>326780.74</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>35080.85</v>
+        <v>788266.33</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>8656.629999999999</v>
+        <v>113737.76</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>7100</v>
+        <v>209889</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>6164.48</v>
+        <v>134088.68</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>7190.6</v>
+        <v>139085.85</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>29111.71</v>
+        <v>596801.29</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>1182.95</v>
+        <v>109138.48</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>2246.77</v>
+        <v>167174.14</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>17202.97</v>
+        <v>135288.72</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>3940.35</v>
+        <v>377876.14</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>24573.04</v>
+        <v>789477.48</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>5327.72</v>
+        <v>85181.96000000001</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>14843.15</v>
+        <v>30910.52</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -19130,78 +18849,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>90.22</v>
+        <v>7231.1</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>9.24</v>
+        <v>6904.18</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>77797.63</v>
+        <v>6495.89</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>612.5599999999999</v>
+        <v>6792.9</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>0</v>
+        <v>7437.76</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>78419.42999999999</v>
+        <v>27630.73</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>143.5</v>
+        <v>7069.9</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>44983.33</v>
+        <v>7034.24</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>458.48</v>
+        <v>7209.64</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>10742.84</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>45585.31</v>
+        <v>32056.62</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>143.5</v>
+        <v>7059.71</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>126861.47</v>
+        <v>7315.32</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>458.48</v>
+        <v>7351.83</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>7751.17</v>
+        <v>6808.32</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>135214.62</v>
+        <v>28535.18</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>205</v>
+        <v>103182.77</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>64147</v>
+        <v>97615.25</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>9216.450000000001</v>
+        <v>-177546.86</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>110.77</v>
+        <v>386321.79</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>73679.22</v>
+        <v>409572.95</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>205</v>
+        <v>93709.35000000001</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>91422.64999999999</v>
+        <v>91886.07000000001</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -19223,78 +18942,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>-540076.34</v>
+        <v>10316.76</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>300042.19</v>
+        <v>9633.33</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>51526.02</v>
+        <v>10783.43</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>-495251.75</v>
+        <v>11943.51</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-40442.19</v>
+        <v>11017.5</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>-184125.73</v>
+        <v>43377.77</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>147518.35</v>
+        <v>15455.79</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-26619.29</v>
+        <v>11241.46</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>-44782.37</v>
+        <v>11390.85</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-237858.81</v>
+        <v>8506.49</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>-161742.12</v>
+        <v>46594.59</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>-19793.14</v>
+        <v>12560.41</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>-731808.1899999999</v>
+        <v>11918.19</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>-44825.63</v>
+        <v>11597.57</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>-657630.63</v>
+        <v>12238.65</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>-1454057.59</v>
+        <v>48314.82</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>383428.87</v>
+        <v>12507.98</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>-417154.8</v>
+        <v>12137.41</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>-128890.42</v>
+        <v>11921.41</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>-199765.2</v>
+        <v>12821.84</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>-362381.55</v>
+        <v>49388.64</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>256723.4</v>
+        <v>11707.12</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>-388537.8</v>
+        <v>12427.34</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -19316,58 +19035,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0</v>
+        <v>59809.67</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>371564.16</v>
+        <v>-51434.55</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0</v>
+        <v>-51879.03</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>0</v>
+        <v>-54912.15</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>0</v>
+        <v>-15171.01</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>371564.16</v>
+        <v>-173396.74</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>2154454.62</v>
+        <v>-52806.03</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>32749.71</v>
+        <v>-34801.84</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>9036.15</v>
-      </c>
-      <c r="P91" s="9" t="n"/>
+        <v>-29351.47</v>
+      </c>
+      <c r="O91" s="18" t="n">
+        <v>-33724.33</v>
+      </c>
+      <c r="P91" s="34" t="n">
+        <v>-150683.67</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>-25539.05</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>-41834.59</v>
+      </c>
       <c r="S91" s="18" t="n">
-        <v>4304.06</v>
-      </c>
-      <c r="U91" s="9" t="n"/>
+        <v>-37308.76</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>-28225.56</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>-132907.96</v>
+      </c>
       <c r="V91" s="18" t="n">
-        <v>100000</v>
+        <v>-96171.84</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>100168</v>
+        <v>-83723.16</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>0</v>
+        <v>-53013.38</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>0</v>
+        <v>-44772.23</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>200168</v>
-      </c>
-      <c r="AB91" s="5" t="n"/>
+        <v>-277680.61</v>
+      </c>
+      <c r="AA91" s="18" t="n">
+        <v>-61617.87</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>-9135.620000000001</v>
+      </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -19388,62 +19128,78 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>사채의증가</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>249261.26</v>
+        <v>390031.95</v>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>-447113.88</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>-95715.22</v>
+      </c>
       <c r="I92" s="18" t="n">
-        <v>0</v>
+        <v>401282.92</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>177631.35</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>36085.17</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>-128460.36</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>-83739.69</v>
+      </c>
       <c r="N92" s="18" t="n">
-        <v>0</v>
+        <v>-89760.59</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
+        <v>-53380.52</v>
+      </c>
+      <c r="P92" s="34" t="n">
+        <v>-355341.16</v>
+      </c>
       <c r="Q92" s="18" t="n">
-        <v>578380.4399999999</v>
+        <v>-72833.17999999999</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>0</v>
+        <v>507010.91</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>0</v>
+        <v>-105491.96</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>299133.46</v>
+        <v>-47148.44</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>877513.9</v>
+        <v>281537.33</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>398851.08</v>
+        <v>-89288.97</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>0</v>
+        <v>146540.07</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>885072.27</v>
+        <v>105710.03</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>945728.41</v>
+        <v>106421.83</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>2229651.76</v>
+        <v>269382.96</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>398861.36</v>
+        <v>-109480.52</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>0</v>
+        <v>67983.59</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -19465,69 +19221,79 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>2482.56</v>
+        <v>102819.66</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>2522.89</v>
+        <v>72229.7</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>82628.41</v>
+        <v>87111.85000000001</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>102778.2</v>
+        <v>101693.09</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>6160.89</v>
+        <v>123706.92</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>194090.39</v>
+        <v>384741.56</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>283.95</v>
+        <v>114720.08</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>3073.77</v>
+        <v>70988.73</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>8480.959999999999</v>
-      </c>
-      <c r="P93" s="9" t="n"/>
+        <v>125619.7</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>67680.85000000001</v>
+      </c>
+      <c r="P93" s="34" t="n">
+        <v>379009.36</v>
+      </c>
       <c r="Q93" s="18" t="n">
-        <v>402822.96</v>
+        <v>55864.07</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>41594.42</v>
+        <v>72825.24000000001</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>7193.09</v>
+        <v>64949.2</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>102606.24</v>
+        <v>64081.33</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>554216.71</v>
+        <v>257719.84</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>141407.31</v>
+        <v>91179.11</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>2247.14</v>
+        <v>46925.54</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>2937.79</v>
+        <v>73752.25999999999</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>12148.98</v>
+        <v>108048.61</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>158741.22</v>
-      </c>
-      <c r="AB93" s="5" t="n"/>
+        <v>319905.52</v>
+      </c>
+      <c r="AA93" s="18" t="n">
+        <v>94238.32000000001</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>83596.02</v>
+      </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -19548,48 +19314,78 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>280000</v>
+        <v>104133.59</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>72627.46000000001</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>89907.98</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>105056.71</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>125439.45</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>393031.6</v>
+      </c>
       <c r="L94" s="18" t="n">
-        <v>200000</v>
+        <v>120787.53</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>150000</v>
+        <v>73053.42999999999</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>0</v>
+        <v>126554.27</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>320000</v>
+        <v>69451.98</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>670000</v>
+        <v>389847.21</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>57157.04</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>74065.75</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>0</v>
+        <v>65508.53</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>170000</v>
-      </c>
-      <c r="U94" s="9" t="n"/>
+        <v>68269.3</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>265000.62</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>92403.92</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>48155.14</v>
+      </c>
       <c r="X94" s="18" t="n">
-        <v>0</v>
+        <v>75674.07000000001</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
+        <v>114486.52</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>330719.65</v>
+      </c>
       <c r="AA94" s="18" t="n">
-        <v>145000</v>
+        <v>95027.00999999999</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>275000</v>
+        <v>84402.91</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -19611,78 +19407,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>6519.81</v>
+        <v>1313.93</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="18" t="n">
-        <v>6289.61</v>
+        <v>397.76</v>
       </c>
       <c r="H95" s="18" t="n">
-        <v>6144.73</v>
+        <v>2796.13</v>
       </c>
       <c r="I95" s="18" t="n">
-        <v>6579.13</v>
+        <v>3363.62</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>6539.68</v>
+        <v>1732.53</v>
       </c>
       <c r="K95" s="34" t="n">
-        <v>25553.15</v>
+        <v>8290.040000000001</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>6312.66</v>
+        <v>6067.45</v>
       </c>
       <c r="M95" s="18" t="n">
-        <v>10488.22</v>
+        <v>2064.7</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>8313.530000000001</v>
+        <v>934.5700000000001</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>9634.780000000001</v>
+        <v>1771.13</v>
       </c>
       <c r="P95" s="34" t="n">
-        <v>34749.19</v>
+        <v>10837.85</v>
       </c>
       <c r="Q95" s="18" t="n">
-        <v>8229.379999999999</v>
+        <v>1292.97</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>8705.33</v>
+        <v>1240.51</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>8786.16</v>
+        <v>559.33</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>8192.6</v>
+        <v>4187.97</v>
       </c>
       <c r="U95" s="34" t="n">
-        <v>33913.47</v>
+        <v>7280.78</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>9113.860000000001</v>
+        <v>1224.81</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>8755.969999999999</v>
+        <v>1229.6</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>8945.84</v>
+        <v>1921.81</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>11242</v>
+        <v>6437.91</v>
       </c>
       <c r="Z95" s="34" t="n">
-        <v>38057.67</v>
+        <v>10814.13</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>10304.71</v>
+        <v>788.6900000000001</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>9825.940000000001</v>
+        <v>806.89</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -19704,78 +19500,70 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>-36812.03</v>
+        <v>806.04</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
-        <v>-44471.1</v>
+        <v>705.9299999999999</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-36900.94</v>
+        <v>2943.72</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>-40517.01</v>
+        <v>508.07</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>-46861.4</v>
+        <v>2019.59</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>-168750.45</v>
+        <v>6177.31</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>-48830.07</v>
-      </c>
-      <c r="M96" s="18" t="n">
-        <v>-66047.39999999999</v>
+        <v>45146.72</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>-59192.81</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>-70323.56</v>
-      </c>
-      <c r="P96" s="34" t="n">
-        <v>-244393.84</v>
-      </c>
+        <v>8482.85</v>
+      </c>
+      <c r="P96" s="9" t="n"/>
       <c r="Q96" s="18" t="n">
-        <v>-50542.72</v>
+        <v>788.05</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>-85058.64999999999</v>
+        <v>820.5700000000001</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>-85128.08</v>
+        <v>1244.14</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>-78992.92999999999</v>
+        <v>4274.97</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>-299722.38</v>
+        <v>7127.73</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>-72092.56</v>
+        <v>336.63</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>-74337.88</v>
+        <v>1113.85</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>-47366.11</v>
+        <v>5295.68</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>-43950.96</v>
+        <v>25821.38</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>-237747.51</v>
+        <v>32567.54</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>-50624.16</v>
+        <v>1031.43</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>-46810.71</v>
+        <v>451.46</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -19797,42 +19585,58 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>2150</v>
+      </c>
       <c r="I97" s="18" t="n">
-        <v>7354.17</v>
+        <v>0</v>
       </c>
       <c r="J97" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K97" s="9" t="n"/>
+      <c r="K97" s="34" t="n">
+        <v>2150.22</v>
+      </c>
       <c r="N97" s="18" t="n">
-        <v>7354.17</v>
+        <v>0.73</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>0</v>
+        <v>8.32</v>
       </c>
       <c r="P97" s="9" t="n"/>
       <c r="S97" s="18" t="n">
-        <v>7354.17</v>
+        <v>3</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="U97" s="9" t="n"/>
+      <c r="V97" s="18" t="n">
+        <v>92.25</v>
+      </c>
       <c r="X97" s="18" t="n">
-        <v>7354.17</v>
+        <v>208.14</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>0</v>
+        <v>75937.03999999999</v>
       </c>
       <c r="Z97" s="9" t="n"/>
-      <c r="AB97" s="5" t="n"/>
+      <c r="AA97" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>0.49</v>
+      </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -19853,78 +19657,78 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>39723.13</v>
+        <v>-732.52</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>-223429.66</v>
+        <v>530.49</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>-7875.24</v>
+        <v>729.63</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>112967.04</v>
+        <v>1381.32</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>354863.67</v>
+        <v>3996.46</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>236525.81</v>
+        <v>6637.9</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>38483.32</v>
+        <v>9399.700000000001</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>154801.38</v>
+        <v>7308.47</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>42356.94</v>
+        <v>8080.09</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>35541.42</v>
+        <v>10292.59</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>271183.06</v>
+        <v>35080.85</v>
       </c>
       <c r="Q98" s="18" t="n">
-        <v>21111.44</v>
+        <v>8656.629999999999</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>-14908.28</v>
+        <v>7100</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>-16228.9</v>
+        <v>6164.48</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>-565693.23</v>
+        <v>7190.6</v>
       </c>
       <c r="U98" s="34" t="n">
-        <v>-575718.97</v>
+        <v>29111.71</v>
       </c>
       <c r="V98" s="18" t="n">
-        <v>403278.38</v>
+        <v>1182.95</v>
       </c>
       <c r="W98" s="18" t="n">
-        <v>-103440.58</v>
+        <v>2246.77</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>112108.32</v>
+        <v>17202.97</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>284532.77</v>
+        <v>3940.35</v>
       </c>
       <c r="Z98" s="34" t="n">
-        <v>696478.89</v>
+        <v>24573.04</v>
       </c>
       <c r="AA98" s="18" t="n">
-        <v>232424.84</v>
+        <v>5327.72</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>-289643.7</v>
+        <v>14843.15</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -19946,78 +19750,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
-        <v>37910.82</v>
+        <v>90.22</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>328395.52</v>
+        <v>9.24</v>
       </c>
       <c r="H99" s="18" t="n">
-        <v>65758.5</v>
+        <v>77797.63</v>
       </c>
       <c r="I99" s="18" t="n">
-        <v>73137.35000000001</v>
+        <v>612.5599999999999</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>309456.3</v>
+        <v>0</v>
       </c>
       <c r="K99" s="34" t="n">
-        <v>776747.67</v>
+        <v>78419.42999999999</v>
       </c>
       <c r="L99" s="18" t="n">
-        <v>830350.62</v>
+        <v>143.5</v>
       </c>
       <c r="M99" s="18" t="n">
-        <v>143259.7</v>
+        <v>44983.33</v>
       </c>
       <c r="N99" s="18" t="n">
-        <v>55829.09</v>
+        <v>458.48</v>
       </c>
       <c r="O99" s="18" t="n">
-        <v>15702.7</v>
+        <v>0</v>
       </c>
       <c r="P99" s="34" t="n">
-        <v>1045142.11</v>
+        <v>45585.31</v>
       </c>
       <c r="Q99" s="18" t="n">
-        <v>1083647.85</v>
+        <v>143.5</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>-11018.16</v>
+        <v>126861.47</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>-31720.07</v>
+        <v>458.48</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>-539579.86</v>
+        <v>7751.17</v>
       </c>
       <c r="U99" s="34" t="n">
-        <v>501329.76</v>
+        <v>135214.62</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>906545.13</v>
+        <v>205</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>-124860.27</v>
+        <v>64147</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>133522.73</v>
+        <v>9216.450000000001</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>278404.85</v>
+        <v>110.77</v>
       </c>
       <c r="Z99" s="34" t="n">
-        <v>1193612.44</v>
+        <v>73679.22</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>1469494.85</v>
+        <v>205</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>-292114.55</v>
+        <v>91422.64999999999</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -20039,29 +19843,79 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>-540076.34</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>81426.66</v>
+        <v>300042.19</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>18467.27</v>
+        <v>51526.02</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>0</v>
+        <v>-495251.75</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>0</v>
+        <v>-40442.19</v>
       </c>
       <c r="K100" s="34" t="n">
-        <v>99893.92999999999</v>
-      </c>
-      <c r="P100" s="9" t="n"/>
-      <c r="U100" s="9" t="n"/>
-      <c r="Z100" s="9" t="n"/>
-      <c r="AB100" s="5" t="n"/>
+        <v>-184125.73</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>147518.35</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>-26619.29</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>-44782.37</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>-237858.81</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>-161742.12</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>-19793.14</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>-731808.1899999999</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>-44825.63</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>-657630.63</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>-1454057.59</v>
+      </c>
+      <c r="V100" s="18" t="n">
+        <v>383428.87</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>-417154.8</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>-128890.42</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>-199765.2</v>
+      </c>
+      <c r="Z100" s="34" t="n">
+        <v>-362381.55</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>256723.4</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>-388537.8</v>
+      </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
       <c r="AE100" s="11" t="n"/>
@@ -20082,35 +19936,57 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>371564.16</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>371564.16</v>
+      </c>
       <c r="L101" s="18" t="n">
-        <v>2106067.64</v>
+        <v>2154454.62</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>71292.67999999999</v>
-      </c>
-      <c r="O101" s="18" t="n">
-        <v>6333.5</v>
+        <v>32749.71</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>9036.15</v>
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="S101" s="18" t="n">
+        <v>4304.06</v>
+      </c>
+      <c r="U101" s="9" t="n"/>
+      <c r="V101" s="18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>100168</v>
+      </c>
+      <c r="X101" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="18" t="n">
-        <v>545592</v>
-      </c>
-      <c r="U101" s="9" t="n"/>
-      <c r="X101" s="18" t="n">
-        <v>958481.46</v>
-      </c>
       <c r="Y101" s="18" t="n">
-        <v>787297.34</v>
-      </c>
-      <c r="Z101" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>200168</v>
+      </c>
       <c r="AB101" s="5" t="n"/>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -20125,6 +20001,750 @@
       <c r="AM101" s="10" t="n"/>
       <c r="AN101" s="10" t="n"/>
       <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>249261.26</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="I102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="9" t="n"/>
+      <c r="N102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="18" t="n">
+        <v>578380.4399999999</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>299133.46</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>877513.9</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>398851.08</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>885072.27</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>945728.41</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>2229651.76</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>398861.36</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>2482.56</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>2522.89</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>82628.41</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>102778.2</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>6160.89</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>194090.39</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>283.95</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>3073.77</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>8480.959999999999</v>
+      </c>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="18" t="n">
+        <v>402822.96</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>41594.42</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>7193.09</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>102606.24</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>554216.71</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>141407.31</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>2247.14</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>2937.79</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>12148.98</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>158741.22</v>
+      </c>
+      <c r="AB103" s="5" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="L104" s="18" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>320000</v>
+      </c>
+      <c r="P104" s="34" t="n">
+        <v>670000</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="18" t="n">
+        <v>170000</v>
+      </c>
+      <c r="U104" s="9" t="n"/>
+      <c r="X104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AA104" s="18" t="n">
+        <v>145000</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>275000</v>
+      </c>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>6519.81</v>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="18" t="n">
+        <v>6289.61</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>6144.73</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>6579.13</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>6539.68</v>
+      </c>
+      <c r="K105" s="34" t="n">
+        <v>25553.15</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>6312.66</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>10488.22</v>
+      </c>
+      <c r="N105" s="18" t="n">
+        <v>8313.530000000001</v>
+      </c>
+      <c r="O105" s="18" t="n">
+        <v>9634.780000000001</v>
+      </c>
+      <c r="P105" s="34" t="n">
+        <v>34749.19</v>
+      </c>
+      <c r="Q105" s="18" t="n">
+        <v>8229.379999999999</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>8705.33</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>8786.16</v>
+      </c>
+      <c r="T105" s="18" t="n">
+        <v>8192.6</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>33913.47</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>9113.860000000001</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>8755.969999999999</v>
+      </c>
+      <c r="X105" s="18" t="n">
+        <v>8945.84</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>11242</v>
+      </c>
+      <c r="Z105" s="34" t="n">
+        <v>38057.67</v>
+      </c>
+      <c r="AA105" s="18" t="n">
+        <v>10304.71</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>9825.940000000001</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>-36812.03</v>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>-44471.1</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>-36900.94</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>-40517.01</v>
+      </c>
+      <c r="J106" s="18" t="n">
+        <v>-46861.4</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>-168750.45</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>-48830.07</v>
+      </c>
+      <c r="M106" s="18" t="n">
+        <v>-66047.39999999999</v>
+      </c>
+      <c r="N106" s="18" t="n">
+        <v>-59192.81</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>-70323.56</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>-244393.84</v>
+      </c>
+      <c r="Q106" s="18" t="n">
+        <v>-50542.72</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>-85058.64999999999</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>-85128.08</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>-78992.92999999999</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>-299722.38</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>-72092.56</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>-74337.88</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>-47366.11</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>-43950.96</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>-237747.51</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>-50624.16</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>-46810.71</v>
+      </c>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="I107" s="18" t="n">
+        <v>7354.17</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="9" t="n"/>
+      <c r="N107" s="18" t="n">
+        <v>7354.17</v>
+      </c>
+      <c r="O107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="9" t="n"/>
+      <c r="S107" s="18" t="n">
+        <v>7354.17</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n"/>
+      <c r="X107" s="18" t="n">
+        <v>7354.17</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9" t="n"/>
+      <c r="AB107" s="5" t="n"/>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>39723.13</v>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>-223429.66</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>-7875.24</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>112967.04</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>354863.67</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>236525.81</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>38483.32</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>154801.38</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>42356.94</v>
+      </c>
+      <c r="O108" s="18" t="n">
+        <v>35541.42</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>271183.06</v>
+      </c>
+      <c r="Q108" s="18" t="n">
+        <v>21111.44</v>
+      </c>
+      <c r="R108" s="18" t="n">
+        <v>-14908.28</v>
+      </c>
+      <c r="S108" s="18" t="n">
+        <v>-16228.9</v>
+      </c>
+      <c r="T108" s="18" t="n">
+        <v>-565693.23</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>-575718.97</v>
+      </c>
+      <c r="V108" s="18" t="n">
+        <v>403278.38</v>
+      </c>
+      <c r="W108" s="18" t="n">
+        <v>-103440.58</v>
+      </c>
+      <c r="X108" s="18" t="n">
+        <v>112108.32</v>
+      </c>
+      <c r="Y108" s="18" t="n">
+        <v>284532.77</v>
+      </c>
+      <c r="Z108" s="34" t="n">
+        <v>696478.89</v>
+      </c>
+      <c r="AA108" s="18" t="n">
+        <v>232424.84</v>
+      </c>
+      <c r="AB108" s="19" t="n">
+        <v>-289643.7</v>
+      </c>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="10" t="n"/>
+      <c r="AL108" s="10" t="n"/>
+      <c r="AM108" s="10" t="n"/>
+      <c r="AN108" s="10" t="n"/>
+      <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>37910.82</v>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="18" t="n">
+        <v>328395.52</v>
+      </c>
+      <c r="H109" s="18" t="n">
+        <v>65758.5</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>73137.35000000001</v>
+      </c>
+      <c r="J109" s="18" t="n">
+        <v>309456.3</v>
+      </c>
+      <c r="K109" s="34" t="n">
+        <v>776747.67</v>
+      </c>
+      <c r="L109" s="18" t="n">
+        <v>830350.62</v>
+      </c>
+      <c r="M109" s="18" t="n">
+        <v>143259.7</v>
+      </c>
+      <c r="N109" s="18" t="n">
+        <v>55829.09</v>
+      </c>
+      <c r="O109" s="18" t="n">
+        <v>15702.7</v>
+      </c>
+      <c r="P109" s="34" t="n">
+        <v>1045142.11</v>
+      </c>
+      <c r="Q109" s="18" t="n">
+        <v>1083647.85</v>
+      </c>
+      <c r="R109" s="18" t="n">
+        <v>-11018.16</v>
+      </c>
+      <c r="S109" s="18" t="n">
+        <v>-31720.07</v>
+      </c>
+      <c r="T109" s="18" t="n">
+        <v>-539579.86</v>
+      </c>
+      <c r="U109" s="34" t="n">
+        <v>501329.76</v>
+      </c>
+      <c r="V109" s="18" t="n">
+        <v>906545.13</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>-124860.27</v>
+      </c>
+      <c r="X109" s="18" t="n">
+        <v>133522.73</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>278404.85</v>
+      </c>
+      <c r="Z109" s="34" t="n">
+        <v>1193612.44</v>
+      </c>
+      <c r="AA109" s="18" t="n">
+        <v>1469494.85</v>
+      </c>
+      <c r="AB109" s="19" t="n">
+        <v>-292114.55</v>
+      </c>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>81426.66</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>18467.27</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="34" t="n">
+        <v>99893.92999999999</v>
+      </c>
+      <c r="P110" s="9" t="n"/>
+      <c r="U110" s="9" t="n"/>
+      <c r="Z110" s="9" t="n"/>
+      <c r="AB110" s="5" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="10" t="n"/>
+      <c r="AL110" s="10" t="n"/>
+      <c r="AM110" s="10" t="n"/>
+      <c r="AN110" s="10" t="n"/>
+      <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+      <c r="L111" s="18" t="n">
+        <v>2106067.64</v>
+      </c>
+      <c r="M111" s="18" t="n">
+        <v>71292.67999999999</v>
+      </c>
+      <c r="O111" s="18" t="n">
+        <v>6333.5</v>
+      </c>
+      <c r="P111" s="9" t="n"/>
+      <c r="S111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>545592</v>
+      </c>
+      <c r="U111" s="9" t="n"/>
+      <c r="X111" s="18" t="n">
+        <v>958481.46</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>787297.34</v>
+      </c>
+      <c r="Z111" s="9" t="n"/>
+      <c r="AB111" s="5" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20385,7 +21005,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42933,7 +43553,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54035.4</v>
+        <v>32561.2</v>
       </c>
     </row>
     <row r="30">
@@ -42953,7 +43573,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.75</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="32">
@@ -42973,7 +43593,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0361</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="34">
@@ -42983,7 +43603,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="35">
@@ -42993,7 +43613,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>599200</v>
+        <v>359500</v>
       </c>
     </row>
     <row r="36">
@@ -43003,7 +43623,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7.26</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4995,7 +4995,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5866,35 +5866,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5985,35 +5985,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6104,35 +6104,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6223,35 +6223,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6342,35 +6342,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6461,35 +6461,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6580,35 +6580,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6699,35 +6699,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6834,7 +6834,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>472000</v>
+        <v>475500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6925,7 +6925,7 @@
         <v>514000</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>474500</v>
+        <v>479000</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -7107,7 +7107,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>471750</v>
+        <v>473000</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9253,10 +9253,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>1103.127470151</v>
+        <v>1103.127470152</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008428074000000001</v>
+        <v>-0.008428075</v>
       </c>
       <c r="AN34" s="30" t="n">
         <v>0.000101345</v>
@@ -9381,10 +9381,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL35" s="30" t="n">
-        <v>1103.127470151</v>
+        <v>1103.127470152</v>
       </c>
       <c r="AM35" s="30" t="n">
-        <v>-0.008428074000000001</v>
+        <v>-0.008428075</v>
       </c>
       <c r="AN35" s="30" t="n">
         <v>0.000101345</v>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>472000</v>
+        <v>475500</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.004351802143125319</v>
+        <v>0.004351802142744159</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.06350866804053873</v>
+        <v>0.06350866803977641</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37255,7 +37255,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45388,7 +45388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.82</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="32">
@@ -45438,7 +45438,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.17</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4995,7 +4995,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5866,35 +5866,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5985,35 +5985,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6104,35 +6104,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6223,35 +6223,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6342,35 +6342,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6461,35 +6461,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6580,35 +6580,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6699,35 +6699,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6834,7 +6834,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>475500</v>
+        <v>469500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7107,7 +7107,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>473000</v>
+        <v>472375</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10553,11 +10553,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>475500</v>
+        <v>469500</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 472,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 472,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37255,7 +37255,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45388,7 +45388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.01</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="32">
@@ -45398,7 +45398,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="33">
@@ -45438,7 +45438,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4995,7 +4995,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -5866,35 +5866,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5985,35 +5985,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6104,35 +6104,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6223,35 +6223,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6342,35 +6342,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6461,35 +6461,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6580,35 +6580,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6699,35 +6699,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6834,7 +6834,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>469500</v>
+        <v>458500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7016,7 +7016,7 @@
         <v>336000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>465000</v>
+        <v>456500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7107,7 +7107,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>472375</v>
+        <v>469200</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10553,11 +10553,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>469500</v>
+        <v>458500</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 472,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 478,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -37255,7 +37255,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45388,7 +45388,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.68</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="32">
@@ -45438,7 +45438,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1795,79 +1795,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN43" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 15,000원 유지</t>
       </text>
     </comment>
-    <comment ref="AI44" authorId="0" shapeId="0">
+    <comment ref="AI43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 15,000원 유지</t>
       </text>
     </comment>
-    <comment ref="AN44" authorId="0" shapeId="0">
+    <comment ref="AN43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 15,000원 유지</t>
@@ -3993,159 +3933,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Y37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AA37" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="AB37" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 28392억 − (비영업손익 36305억 − 12분기 기준선 -235억) × (1 − 24.4%, 분기 유효세율(법인세 9166억 ÷ 세전 37594억)) × 지배 비중 1.00(그 분기 지배NI/NI) = 761억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 386,060.8원</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 36,539억 × (1 − 세율 24.4% [분기 유효세율(법인세 9166억 ÷ 세전 37594억)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = 761억 ÷ 유통주식수 · 초과 = 비영업손익 36,305억 − 12분기 기준선 -235억 · 보고 EPS 386,061원(EPS 행 불변) · 상수 27630.69·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN37" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC38" authorId="0" shapeId="0">
@@ -4979,7 +4829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4995,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5033,7 +4883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -5158,52 +5008,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 386,061→조정 10,347원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 3.7배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/002380.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/002380.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 32.2% &gt; 추세 3.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.63 유의)): 전년동기 × (1+g) 추세 / 일회성 의심 2026Q2: 비영업손익 36,305억(영업이익 1,289억의 28배, 12분기 중위 2,244억·기준선 -235억) → 지배NI 28,392억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 10,346.6원(보고 386,060.8원; 초과 비영업손익 36,539억 × (1 − 세율 24.4%) × 지배 비중 1.00 = 27,631억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +7150.0억이 이자손익 추정 -722.7억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +3643/+8610/+2013/+36364(중위 +6127억) → 추정 2026Q3 -723억(차 -6849억, -112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 3.6, "op_wape_pct": 21.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 22.5, "wape_trend": 3.9, "adopted": false, "decision": "rejected"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 16578.27, "rev_act": 16228.33, "op_pred": 1094.05, "op_act": 1172.64}, {"q": "2025Q4", "rev_pred": 16814.11, "rev_act": 15564.18, "op_pred": 1109.62, "op_act": 665.27}, {"q": "2026Q1", "rev_pred": 16224.2, "rev_act": 16264.0, "op_pred": 1070.69, "op_act": 881.28}, {"q": "2026Q2", "rev_pred": 17299.1, "rev_act": 18060.19, "op_pred": 1141.62, "op_act": 1288.84}]}</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 32.2% &gt; 추세 3.6% × 1.10 (suppliers_mentions·시차 4·4분기 이동합·창 12, r=0.63 유의)): 전년동기 × (1+g) 추세 / 일회성 의심 2026Q2: 비영업손익 36,305억(영업이익 1,289억의 28배, 12분기 중위 2,244억·기준선 -235억) → 지배NI 28,392억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS 10,346.6원(보고 386,060.8원; 초과 비영업손익 36,539억 × (1 − 세율 24.4%) × 지배 비중 1.00 = 27,631억 차감 — 추정, 조정EPS 행) / 기타금융손익(금융손익 − 이자 − 외환 − 파생 잔차) 최근 4분기 중위 +7150.0억이 이자손익 추정 -722.7억의 50% 초과 → 추정 0 — 평가손익·재분류 여부는 주석 확인 / 금융손익 실적→추정 단절: 최근 4분기 실적 +3643/+8610/+2013/+36364(중위 +6127억) → 추정 2026Q3 -723억(차 -6849억, -112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 32.2, "op_wape_pct": 43.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": 3.9, "adopted": "undetermined", "decision": "undetermined", "note": "현재 채택 조합(suppliers_mentions·시차 4·ma4·창 8)을 동결 데이터로 재적합할 수 없음(짝·고객 모델 부족) → 연동 WAPE 없음, undetermined(유의성 조건만으로 채택)"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 20450.78, "rev_act": 16228.33, "op_pred": 1349.61, "op_act": 1172.64}, {"q": "2025Q4", "rev_pred": 21141.06, "rev_act": 15564.18, "op_pred": 1395.17, "op_act": 665.27}, {"q": "2026Q1", "rev_pred": 21947.17, "rev_act": 16264.0, "op_pred": 1448.37, "op_act": 881.28}, {"q": "2026Q2", "rev_pred": 23848.0, "rev_act": 18060.19, "op_pred": 1573.81, "op_act": 1288.84}]}</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7405,11 +7262,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -7417,19 +7274,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -7437,19 +7294,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -8500,11 +8357,11 @@
         <v/>
       </c>
       <c r="AC29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AD29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AE29" s="25">
@@ -8512,19 +8369,19 @@
         <v/>
       </c>
       <c r="AF29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AG29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AH29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AI29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AJ29" s="25">
@@ -8532,19 +8389,19 @@
         <v/>
       </c>
       <c r="AK29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AL29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AM29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AN29" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AO29" s="25">
@@ -8665,11 +8522,11 @@
         <v/>
       </c>
       <c r="AC30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AD30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AE30" s="25">
@@ -8677,19 +8534,19 @@
         <v/>
       </c>
       <c r="AF30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AG30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AH30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AI30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AJ30" s="25">
@@ -8697,19 +8554,19 @@
         <v/>
       </c>
       <c r="AK30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AL30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AM30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AN30" s="26">
-        <f>$D$56</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="AO30" s="25">
@@ -9253,10 +9110,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>1103.127470152</v>
+        <v>1103.127470151</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008428075</v>
+        <v>-0.008428074000000001</v>
       </c>
       <c r="AN34" s="30" t="n">
         <v>0.000101345</v>
@@ -9381,10 +9238,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL35" s="30" t="n">
-        <v>1103.127470152</v>
+        <v>1103.127470151</v>
       </c>
       <c r="AM35" s="30" t="n">
-        <v>-0.008428075</v>
+        <v>-0.008428074000000001</v>
       </c>
       <c r="AN35" s="30" t="n">
         <v>0.000101345</v>
@@ -10232,264 +10089,176 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21">
-        <f>IFERROR(subQ!J37/subQ!E37-1,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="22" t="n"/>
-      <c r="L43" s="21">
-        <f>IFERROR(subQ!L37/subQ!G37-1,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="21">
-        <f>IFERROR(subQ!M37/subQ!H37-1,"")</f>
-        <v/>
-      </c>
-      <c r="N43" s="21">
-        <f>IFERROR(subQ!N37/subQ!I37-1,"")</f>
-        <v/>
-      </c>
-      <c r="O43" s="21">
-        <f>IFERROR(subQ!O37/subQ!J37-1,"")</f>
-        <v/>
-      </c>
-      <c r="P43" s="22" t="n"/>
-      <c r="Q43" s="21">
-        <f>IFERROR(subQ!Q37/subQ!L37-1,"")</f>
-        <v/>
-      </c>
-      <c r="R43" s="21">
-        <f>IFERROR(subQ!R37/subQ!M37-1,"")</f>
-        <v/>
-      </c>
-      <c r="S43" s="21">
-        <f>IFERROR(subQ!S37/subQ!N37-1,"")</f>
-        <v/>
-      </c>
-      <c r="T43" s="21">
-        <f>IFERROR(subQ!T37/subQ!O37-1,"")</f>
-        <v/>
-      </c>
-      <c r="U43" s="22" t="n"/>
-      <c r="V43" s="21">
-        <f>IFERROR(subQ!V37/subQ!Q37-1,"")</f>
-        <v/>
-      </c>
-      <c r="W43" s="21">
-        <f>IFERROR(subQ!W37/subQ!R37-1,"")</f>
-        <v/>
-      </c>
-      <c r="X43" s="21">
-        <f>IFERROR(subQ!X37/subQ!S37-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y43" s="21">
-        <f>IFERROR(subQ!Y37/subQ!T37-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z43" s="22" t="n"/>
-      <c r="AA43" s="21">
-        <f>IFERROR(subQ!AA37/subQ!V37-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB43" s="23">
-        <f>IFERROR(subQ!AB37/subQ!W37-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC43" s="24" t="n">
-        <v>-0.902029539</v>
-      </c>
-      <c r="AD43" s="24" t="n">
-        <v>-0.896413319</v>
-      </c>
-      <c r="AE43" s="25" t="n"/>
-      <c r="AF43" s="24" t="n">
-        <v>-0.851500956</v>
-      </c>
-      <c r="AG43" s="24" t="n">
-        <v>-0.450650455</v>
-      </c>
-      <c r="AH43" s="24" t="n">
-        <v>0.004140406</v>
-      </c>
-      <c r="AI43" s="24" t="n">
-        <v>0.00449473</v>
-      </c>
-      <c r="AJ43" s="25" t="n"/>
-      <c r="AK43" s="24" t="n">
-        <v>0.004108745</v>
-      </c>
-      <c r="AL43" s="24" t="n">
-        <v>0.003430743</v>
-      </c>
-      <c r="AM43" s="24" t="n">
-        <v>0.002542722</v>
-      </c>
-      <c r="AN43" s="24" t="n">
-        <v>0.002777349</v>
-      </c>
-      <c r="AO43" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E43" s="27">
+        <f>subQ!E39</f>
+        <v/>
+      </c>
+      <c r="F43" s="28">
+        <f>subQ!F39</f>
+        <v/>
+      </c>
+      <c r="G43" s="27">
+        <f>subQ!G39</f>
+        <v/>
+      </c>
+      <c r="H43" s="27">
+        <f>subQ!H39</f>
+        <v/>
+      </c>
+      <c r="I43" s="27">
+        <f>subQ!I39</f>
+        <v/>
+      </c>
+      <c r="J43" s="27">
+        <f>subQ!J39</f>
+        <v/>
+      </c>
+      <c r="K43" s="28">
+        <f>subQ!K39</f>
+        <v/>
+      </c>
+      <c r="L43" s="27">
+        <f>subQ!L39</f>
+        <v/>
+      </c>
+      <c r="M43" s="27">
+        <f>subQ!M39</f>
+        <v/>
+      </c>
+      <c r="N43" s="27">
+        <f>subQ!N39</f>
+        <v/>
+      </c>
+      <c r="O43" s="27">
+        <f>subQ!O39</f>
+        <v/>
+      </c>
+      <c r="P43" s="28">
+        <f>subQ!P39</f>
+        <v/>
+      </c>
+      <c r="Q43" s="27">
+        <f>subQ!Q39</f>
+        <v/>
+      </c>
+      <c r="R43" s="27">
+        <f>subQ!R39</f>
+        <v/>
+      </c>
+      <c r="S43" s="27">
+        <f>subQ!S39</f>
+        <v/>
+      </c>
+      <c r="T43" s="27">
+        <f>subQ!T39</f>
+        <v/>
+      </c>
+      <c r="U43" s="28">
+        <f>subQ!U39</f>
+        <v/>
+      </c>
+      <c r="V43" s="27">
+        <f>subQ!V39</f>
+        <v/>
+      </c>
+      <c r="W43" s="27">
+        <f>subQ!W39</f>
+        <v/>
+      </c>
+      <c r="X43" s="27">
+        <f>subQ!X39</f>
+        <v/>
+      </c>
+      <c r="Y43" s="27">
+        <f>subQ!Y39</f>
+        <v/>
+      </c>
+      <c r="Z43" s="28">
+        <f>subQ!Z39</f>
+        <v/>
+      </c>
+      <c r="AA43" s="27">
+        <f>subQ!AA39</f>
+        <v/>
+      </c>
+      <c r="AB43" s="29">
+        <f>subQ!AB39</f>
+        <v/>
+      </c>
+      <c r="AC43" s="32" t="n"/>
+      <c r="AD43" s="30" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AE43" s="31">
+        <f>subQ!AE39</f>
+        <v/>
+      </c>
+      <c r="AF43" s="32" t="n"/>
+      <c r="AG43" s="32" t="n"/>
+      <c r="AH43" s="32" t="n"/>
+      <c r="AI43" s="30" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AJ43" s="31">
+        <f>subQ!AJ39</f>
+        <v/>
+      </c>
+      <c r="AK43" s="32" t="n"/>
+      <c r="AL43" s="32" t="n"/>
+      <c r="AM43" s="32" t="n"/>
+      <c r="AN43" s="30" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AO43" s="31">
+        <f>subQ!AO39</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E44" s="27">
-        <f>subQ!E39</f>
-        <v/>
-      </c>
-      <c r="F44" s="28">
-        <f>subQ!F39</f>
-        <v/>
-      </c>
-      <c r="G44" s="27">
-        <f>subQ!G39</f>
-        <v/>
-      </c>
-      <c r="H44" s="27">
-        <f>subQ!H39</f>
-        <v/>
-      </c>
-      <c r="I44" s="27">
-        <f>subQ!I39</f>
-        <v/>
-      </c>
-      <c r="J44" s="27">
-        <f>subQ!J39</f>
-        <v/>
-      </c>
-      <c r="K44" s="28">
-        <f>subQ!K39</f>
-        <v/>
-      </c>
-      <c r="L44" s="27">
-        <f>subQ!L39</f>
-        <v/>
-      </c>
-      <c r="M44" s="27">
-        <f>subQ!M39</f>
-        <v/>
-      </c>
-      <c r="N44" s="27">
-        <f>subQ!N39</f>
-        <v/>
-      </c>
-      <c r="O44" s="27">
-        <f>subQ!O39</f>
-        <v/>
-      </c>
-      <c r="P44" s="28">
-        <f>subQ!P39</f>
-        <v/>
-      </c>
-      <c r="Q44" s="27">
-        <f>subQ!Q39</f>
-        <v/>
-      </c>
-      <c r="R44" s="27">
-        <f>subQ!R39</f>
-        <v/>
-      </c>
-      <c r="S44" s="27">
-        <f>subQ!S39</f>
-        <v/>
-      </c>
-      <c r="T44" s="27">
-        <f>subQ!T39</f>
-        <v/>
-      </c>
-      <c r="U44" s="28">
-        <f>subQ!U39</f>
-        <v/>
-      </c>
-      <c r="V44" s="27">
-        <f>subQ!V39</f>
-        <v/>
-      </c>
-      <c r="W44" s="27">
-        <f>subQ!W39</f>
-        <v/>
-      </c>
-      <c r="X44" s="27">
-        <f>subQ!X39</f>
-        <v/>
-      </c>
-      <c r="Y44" s="27">
-        <f>subQ!Y39</f>
-        <v/>
-      </c>
-      <c r="Z44" s="28">
-        <f>subQ!Z39</f>
-        <v/>
-      </c>
-      <c r="AA44" s="27">
-        <f>subQ!AA39</f>
-        <v/>
-      </c>
-      <c r="AB44" s="29">
-        <f>subQ!AB39</f>
-        <v/>
-      </c>
-      <c r="AC44" s="32" t="n"/>
-      <c r="AD44" s="30" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AE44" s="31">
-        <f>subQ!AE39</f>
-        <v/>
-      </c>
-      <c r="AF44" s="32" t="n"/>
-      <c r="AG44" s="32" t="n"/>
-      <c r="AH44" s="32" t="n"/>
-      <c r="AI44" s="30" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AJ44" s="31">
-        <f>subQ!AJ39</f>
-        <v/>
-      </c>
-      <c r="AK44" s="32" t="n"/>
-      <c r="AL44" s="32" t="n"/>
-      <c r="AM44" s="32" t="n"/>
-      <c r="AN44" s="30" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AO44" s="31">
-        <f>subQ!AO39</f>
-        <v/>
-      </c>
+      <c r="F44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+      <c r="P44" s="9" t="n"/>
+      <c r="U44" s="9" t="n"/>
+      <c r="Z44" s="9" t="n"/>
+      <c r="AB44" s="5" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="11" t="n"/>
+      <c r="AK44" s="10" t="n"/>
+      <c r="AL44" s="10" t="n"/>
+      <c r="AM44" s="10" t="n"/>
+      <c r="AN44" s="10" t="n"/>
+      <c r="AO44" s="11" t="n"/>
     </row>
     <row r="45">
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
@@ -10511,14 +10280,22 @@
       <c r="AO45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="n">
+        <v>458500</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 478,000원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10544,20 +10321,22 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D47" s="34" t="n">
-        <v>458500</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 478,000원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10583,22 +10362,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D48" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -10624,20 +10401,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 3.7배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -10663,20 +10440,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D50" s="30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 3.7배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -10702,20 +10479,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D51" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -10741,20 +10518,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>20</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -10780,20 +10557,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D53" s="36" t="n">
+        <v>0.2200009445546425</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 29.8% 가 5~27% 밖; 세전 &gt; 0 분기 중위 31.2% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -10819,20 +10596,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200009445546425</v>
+        <v>0.18873975011067</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 29.8% 가 5~27% 밖; 세전 &gt; 0 분기 중위 31.2% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1887)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -10858,20 +10635,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.18873975011067</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1887)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10897,20 +10674,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>1</v>
+        <v>0.004351802143125319</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0043)</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10936,20 +10713,20 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.004351802142744159</v>
+        <v>0.06350866804053873</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0043)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0635)</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10975,20 +10752,20 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D58" s="36" t="n">
-        <v>0.06350866803977641</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="n">
+        <v>0.0717</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0635)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -11014,20 +10791,18 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="n">
-        <v>0.0717</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
@@ -11053,18 +10828,18 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D60" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F60" s="9" t="n"/>
@@ -11090,15 +10865,15 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="n"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -11123,43 +10898,6 @@
       <c r="AM61" s="10" t="n"/>
       <c r="AN61" s="10" t="n"/>
       <c r="AO61" s="11" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="n"/>
-      <c r="K62" s="9" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="U62" s="9" t="n"/>
-      <c r="Z62" s="9" t="n"/>
-      <c r="AB62" s="5" t="n"/>
-      <c r="AC62" s="10" t="n"/>
-      <c r="AD62" s="10" t="n"/>
-      <c r="AE62" s="11" t="n"/>
-      <c r="AF62" s="10" t="n"/>
-      <c r="AG62" s="10" t="n"/>
-      <c r="AH62" s="10" t="n"/>
-      <c r="AI62" s="10" t="n"/>
-      <c r="AJ62" s="11" t="n"/>
-      <c r="AK62" s="10" t="n"/>
-      <c r="AL62" s="10" t="n"/>
-      <c r="AM62" s="10" t="n"/>
-      <c r="AN62" s="10" t="n"/>
-      <c r="AO62" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11421,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21453,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31579,11 +31317,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB31*변수!$D$57-AB29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AB31*변수!$D$56-AB29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC31*변수!$D$57-AC29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AC31*변수!$D$56-AC29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -31591,19 +31329,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD31*변수!$D$57-AD29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AD31*변수!$D$56-AD29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF31*변수!$D$57-AF29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AF31*변수!$D$56-AF29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG31*변수!$D$57-AG29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AG31*변수!$D$56-AG29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH31*변수!$D$57-AH29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AH31*변수!$D$56-AH29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -31611,19 +31349,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI31*변수!$D$57-AI29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AI31*변수!$D$56-AI29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK31*변수!$D$57-AK29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AK31*변수!$D$56-AK29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL31*변수!$D$57-AL29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AL31*변수!$D$56-AL29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM31*변수!$D$57-AM29*변수!$D$58)/4,"")</f>
+        <f>IFERROR((AM31*변수!$D$56-AM29*변수!$D$57)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -35496,86 +35234,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E37" s="18" t="n">
-        <v>-24107.2</v>
+      <c r="E37" s="18">
+        <f>IFERROR(E36,"")</f>
+        <v/>
       </c>
       <c r="F37" s="37" t="n"/>
-      <c r="G37" s="18" t="n">
-        <v>888.2</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>23028.8</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>-36443.1</v>
-      </c>
-      <c r="J37" s="18" t="n">
-        <v>17124.1</v>
+      <c r="G37" s="18">
+        <f>IFERROR(G36,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="18">
+        <f>IFERROR(H36,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>IFERROR(I36,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="18">
+        <f>IFERROR(J36,"")</f>
+        <v/>
       </c>
       <c r="K37" s="37">
         <f>SUM(G37:J37)</f>
         <v/>
       </c>
-      <c r="L37" s="18" t="n">
-        <v>1106.4</v>
-      </c>
-      <c r="M37" s="18" t="n">
-        <v>12373</v>
-      </c>
-      <c r="N37" s="18" t="n">
-        <v>6386</v>
-      </c>
-      <c r="O37" s="18" t="n">
-        <v>9051.9</v>
+      <c r="L37" s="18">
+        <f>IFERROR(L36,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="18">
+        <f>IFERROR(M36,"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="18">
+        <f>IFERROR(N36,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="18">
+        <f>IFERROR(O36,"")</f>
+        <v/>
       </c>
       <c r="P37" s="37">
         <f>SUM(L37:O37)</f>
         <v/>
       </c>
-      <c r="Q37" s="18" t="n">
-        <v>64206.3</v>
-      </c>
-      <c r="R37" s="18" t="n">
-        <v>-4465.6</v>
-      </c>
-      <c r="S37" s="18" t="n">
-        <v>-5752.9</v>
-      </c>
-      <c r="T37" s="18" t="n">
-        <v>-11757.7</v>
+      <c r="Q37" s="18">
+        <f>IFERROR(Q36,"")</f>
+        <v/>
+      </c>
+      <c r="R37" s="18">
+        <f>IFERROR(R36,"")</f>
+        <v/>
+      </c>
+      <c r="S37" s="18">
+        <f>IFERROR(S36,"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="18">
+        <f>IFERROR(T36,"")</f>
+        <v/>
       </c>
       <c r="U37" s="37">
         <f>SUM(Q37:T37)</f>
         <v/>
       </c>
-      <c r="V37" s="18" t="n">
-        <v>5989.8</v>
-      </c>
-      <c r="W37" s="18" t="n">
-        <v>121464.5</v>
-      </c>
-      <c r="X37" s="18" t="n">
-        <v>44374.6</v>
-      </c>
-      <c r="Y37" s="18" t="n">
-        <v>37371.6</v>
+      <c r="V37" s="18">
+        <f>IFERROR(V36,"")</f>
+        <v/>
+      </c>
+      <c r="W37" s="18">
+        <f>IFERROR(W36,"")</f>
+        <v/>
+      </c>
+      <c r="X37" s="18">
+        <f>IFERROR(X36,"")</f>
+        <v/>
+      </c>
+      <c r="Y37" s="18">
+        <f>IFERROR(Y36,"")</f>
+        <v/>
       </c>
       <c r="Z37" s="37">
         <f>SUM(V37:Y37)</f>
         <v/>
       </c>
-      <c r="AA37" s="18" t="n">
-        <v>29501.2</v>
-      </c>
-      <c r="AB37" s="39" t="n">
-        <v>10346.6</v>
+      <c r="AA37" s="18">
+        <f>IFERROR(AA36,"")</f>
+        <v/>
+      </c>
+      <c r="AB37" s="39">
+        <f>IFERROR((AB21-(27630.69)*(1.0))*100/AB35,"")</f>
+        <v/>
       </c>
       <c r="AC37" s="20">
-        <f>IFERROR(X37*(1+변수!AC43),"")</f>
+        <f>IFERROR(AC36,"")</f>
         <v/>
       </c>
       <c r="AD37" s="20">
-        <f>IFERROR(Y37*(1+변수!AD43),"")</f>
+        <f>IFERROR(AD36,"")</f>
         <v/>
       </c>
       <c r="AE37" s="38">
@@ -35583,19 +35340,19 @@
         <v/>
       </c>
       <c r="AF37" s="20">
-        <f>IFERROR(AA37*(1+변수!AF43),"")</f>
+        <f>IFERROR(AF36,"")</f>
         <v/>
       </c>
       <c r="AG37" s="20">
-        <f>IFERROR(AB37*(1+변수!AG43),"")</f>
+        <f>IFERROR(AG36,"")</f>
         <v/>
       </c>
       <c r="AH37" s="20">
-        <f>IFERROR(AC37*(1+변수!AH43),"")</f>
+        <f>IFERROR(AH36,"")</f>
         <v/>
       </c>
       <c r="AI37" s="20">
-        <f>IFERROR(AD37*(1+변수!AI43),"")</f>
+        <f>IFERROR(AI36,"")</f>
         <v/>
       </c>
       <c r="AJ37" s="38">
@@ -35603,19 +35360,19 @@
         <v/>
       </c>
       <c r="AK37" s="20">
-        <f>IFERROR(AF37*(1+변수!AK43),"")</f>
+        <f>IFERROR(AK36,"")</f>
         <v/>
       </c>
       <c r="AL37" s="20">
-        <f>IFERROR(AG37*(1+변수!AL43),"")</f>
+        <f>IFERROR(AL36,"")</f>
         <v/>
       </c>
       <c r="AM37" s="20">
-        <f>IFERROR(AH37*(1+변수!AM43),"")</f>
+        <f>IFERROR(AM36,"")</f>
         <v/>
       </c>
       <c r="AN37" s="20">
-        <f>IFERROR(AI37*(1+변수!AN43),"")</f>
+        <f>IFERROR(AN36,"")</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -35864,7 +35621,7 @@
       <c r="AB39" s="19" t="n"/>
       <c r="AC39" s="20" t="n"/>
       <c r="AD39" s="20">
-        <f>변수!AD44</f>
+        <f>변수!AD43</f>
         <v/>
       </c>
       <c r="AE39" s="38">
@@ -35875,7 +35632,7 @@
       <c r="AG39" s="20" t="n"/>
       <c r="AH39" s="20" t="n"/>
       <c r="AI39" s="20">
-        <f>변수!AI44</f>
+        <f>변수!AI43</f>
         <v/>
       </c>
       <c r="AJ39" s="38">
@@ -35886,7 +35643,7 @@
       <c r="AL39" s="20" t="n"/>
       <c r="AM39" s="20" t="n"/>
       <c r="AN39" s="20">
-        <f>변수!AN44</f>
+        <f>변수!AN43</f>
         <v/>
       </c>
       <c r="AO39" s="38">
@@ -35994,11 +35751,11 @@
         <v/>
       </c>
       <c r="AC40" s="40">
-        <f>IFERROR(변수!$D$47/(Y36+AA36+AB36+AC36),"")</f>
+        <f>IFERROR(변수!$D$46/(Y36+AA36+AB36+AC36),"")</f>
         <v/>
       </c>
       <c r="AD40" s="40">
-        <f>IFERROR(변수!$D$47/(AA36+AB36+AC36+AD36),"")</f>
+        <f>IFERROR(변수!$D$46/(AA36+AB36+AC36+AD36),"")</f>
         <v/>
       </c>
       <c r="AE40" s="41">
@@ -36006,19 +35763,19 @@
         <v/>
       </c>
       <c r="AF40" s="40">
-        <f>IFERROR(변수!$D$47/(AB36+AC36+AD36+AF36),"")</f>
+        <f>IFERROR(변수!$D$46/(AB36+AC36+AD36+AF36),"")</f>
         <v/>
       </c>
       <c r="AG40" s="40">
-        <f>IFERROR(변수!$D$47/(AC36+AD36+AF36+AG36),"")</f>
+        <f>IFERROR(변수!$D$46/(AC36+AD36+AF36+AG36),"")</f>
         <v/>
       </c>
       <c r="AH40" s="40">
-        <f>IFERROR(변수!$D$47/(AD36+AF36+AG36+AH36),"")</f>
+        <f>IFERROR(변수!$D$46/(AD36+AF36+AG36+AH36),"")</f>
         <v/>
       </c>
       <c r="AI40" s="40">
-        <f>IFERROR(변수!$D$47/(AF36+AG36+AH36+AI36),"")</f>
+        <f>IFERROR(변수!$D$46/(AF36+AG36+AH36+AI36),"")</f>
         <v/>
       </c>
       <c r="AJ40" s="41">
@@ -36026,19 +35783,19 @@
         <v/>
       </c>
       <c r="AK40" s="40">
-        <f>IFERROR(변수!$D$47/(AG36+AH36+AI36+AK36),"")</f>
+        <f>IFERROR(변수!$D$46/(AG36+AH36+AI36+AK36),"")</f>
         <v/>
       </c>
       <c r="AL40" s="40">
-        <f>IFERROR(변수!$D$47/(AH36+AI36+AK36+AL36),"")</f>
+        <f>IFERROR(변수!$D$46/(AH36+AI36+AK36+AL36),"")</f>
         <v/>
       </c>
       <c r="AM40" s="40">
-        <f>IFERROR(변수!$D$47/(AI36+AK36+AL36+AM36),"")</f>
+        <f>IFERROR(변수!$D$46/(AI36+AK36+AL36+AM36),"")</f>
         <v/>
       </c>
       <c r="AN40" s="40">
-        <f>IFERROR(변수!$D$47/(AK36+AL36+AM36+AN36),"")</f>
+        <f>IFERROR(변수!$D$46/(AK36+AL36+AM36+AN36),"")</f>
         <v/>
       </c>
       <c r="AO40" s="41">
@@ -36164,11 +35921,11 @@
         <v/>
       </c>
       <c r="AC41" s="40">
-        <f>IFERROR(변수!$D$47/AC38,"")</f>
+        <f>IFERROR(변수!$D$46/AC38,"")</f>
         <v/>
       </c>
       <c r="AD41" s="40">
-        <f>IFERROR(변수!$D$47/AD38,"")</f>
+        <f>IFERROR(변수!$D$46/AD38,"")</f>
         <v/>
       </c>
       <c r="AE41" s="41">
@@ -36176,19 +35933,19 @@
         <v/>
       </c>
       <c r="AF41" s="40">
-        <f>IFERROR(변수!$D$47/AF38,"")</f>
+        <f>IFERROR(변수!$D$46/AF38,"")</f>
         <v/>
       </c>
       <c r="AG41" s="40">
-        <f>IFERROR(변수!$D$47/AG38,"")</f>
+        <f>IFERROR(변수!$D$46/AG38,"")</f>
         <v/>
       </c>
       <c r="AH41" s="40">
-        <f>IFERROR(변수!$D$47/AH38,"")</f>
+        <f>IFERROR(변수!$D$46/AH38,"")</f>
         <v/>
       </c>
       <c r="AI41" s="40">
-        <f>IFERROR(변수!$D$47/AI38,"")</f>
+        <f>IFERROR(변수!$D$46/AI38,"")</f>
         <v/>
       </c>
       <c r="AJ41" s="41">
@@ -36196,19 +35953,19 @@
         <v/>
       </c>
       <c r="AK41" s="40">
-        <f>IFERROR(변수!$D$47/AK38,"")</f>
+        <f>IFERROR(변수!$D$46/AK38,"")</f>
         <v/>
       </c>
       <c r="AL41" s="40">
-        <f>IFERROR(변수!$D$47/AL38,"")</f>
+        <f>IFERROR(변수!$D$46/AL38,"")</f>
         <v/>
       </c>
       <c r="AM41" s="40">
-        <f>IFERROR(변수!$D$47/AM38,"")</f>
+        <f>IFERROR(변수!$D$46/AM38,"")</f>
         <v/>
       </c>
       <c r="AN41" s="40">
-        <f>IFERROR(변수!$D$47/AN38,"")</f>
+        <f>IFERROR(변수!$D$46/AN38,"")</f>
         <v/>
       </c>
       <c r="AO41" s="41">
@@ -37242,7 +36999,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="W2" s="43" t="n"/>
@@ -43015,7 +42772,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="I2" s="43" t="n"/>
@@ -45002,7 +44759,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -45013,7 +44770,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
     </row>
@@ -45190,7 +44947,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D53+F7*(1-변수!D53),"")</f>
+        <f>IFERROR(E7*변수!D52+F7*(1-변수!D52),"")</f>
         <v/>
       </c>
     </row>
@@ -45201,7 +44958,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D50</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -45225,7 +44982,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D51</f>
+        <f>변수!D50</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -45249,7 +45006,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D52</f>
+        <f>변수!D51</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -45313,7 +45070,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
     </row>
@@ -47124,7 +46881,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D60</f>
+        <f>변수!D59</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>458500</v>
+        <v>457000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>469200</v>
+        <v>468900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9110,10 +9110,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>1103.127470151</v>
+        <v>1103.127470152</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008428074000000001</v>
+        <v>-0.008428075</v>
       </c>
       <c r="AN34" s="30" t="n">
         <v>0.000101345</v>
@@ -9238,10 +9238,10 @@
         <v>0.0011091</v>
       </c>
       <c r="AL35" s="30" t="n">
-        <v>1103.127470151</v>
+        <v>1103.127470152</v>
       </c>
       <c r="AM35" s="30" t="n">
-        <v>-0.008428074000000001</v>
+        <v>-0.008428075</v>
       </c>
       <c r="AN35" s="30" t="n">
         <v>0.000101345</v>
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>458500</v>
+        <v>457000</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 478,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 467,500원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.004351802143125319</v>
+        <v>0.004351802142744159</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.06350866804053873</v>
+        <v>0.06350866803977641</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.08</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>457000</v>
+        <v>455000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6873,7 +6873,7 @@
         <v>336000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>456500</v>
+        <v>452000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>468900</v>
+        <v>466583.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10291,7 +10291,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>457000</v>
+        <v>455000</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="32">
@@ -45155,7 +45155,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.029999999999999</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>455000</v>
+        <v>434000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6873,7 +6873,7 @@
         <v>336000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>452000</v>
+        <v>419500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>466583.3</v>
+        <v>461357.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>455000</v>
+        <v>434000</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 467,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 460,500원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.89</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="32">
@@ -45155,7 +45155,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="33">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.01</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>434000</v>
+        <v>438500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>461357.1</v>
+        <v>458312.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>434000</v>
+        <v>438500</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 460,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 455,500원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.74</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="32">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.83</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>438500</v>
+        <v>428500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6873,7 +6873,7 @@
         <v>336000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>419500</v>
+        <v>407000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>458312.5</v>
+        <v>449000</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>438500</v>
+        <v>428500</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 455,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 417,500원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.98</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="32">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.869999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/002380_model.xlsx
+++ b/argus/kship/models/002380_model.xlsx
@@ -4845,7 +4845,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5723,35 +5723,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5842,35 +5842,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5961,35 +5961,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6080,35 +6080,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6199,35 +6199,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6318,35 +6318,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6437,35 +6437,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6556,35 +6556,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6691,7 +6691,7 @@
         <v>470500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>428500</v>
+        <v>368000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6873,7 +6873,7 @@
         <v>336000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>407000</v>
+        <v>368000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6964,7 +6964,7 @@
         <v>451483.9</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>449000</v>
+        <v>427906.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10291,11 +10291,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>428500</v>
+        <v>368000</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 417,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 384,500원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45145,7 +45145,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.44</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="32">
@@ -45155,7 +45155,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.779999999999999</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="37">
